--- a/results/job_matches_2026-06-23.xlsx
+++ b/results/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0394f69da3f3e0c</t>
         </is>
       </c>
     </row>
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c56ac0ca901604</t>
+          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Backend Developer (Data Layer / API Specialist)</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425ea68f605d30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c56ac0ca901604</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Houston Only</t>
+          <t>Backend Developer (Data Layer / API Specialist)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=425ea68f605d30dd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f0995774c98d8f64</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer - Houston Only</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brownsville, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
+          <t>Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, S3, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
+          <t>https://www.indeed.com/viewjob?jk=1489cddaebca9c0c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Brownsville, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
+          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amy's Kitchen</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Linux Systems Administrator - Senior</t>
+          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95ae15fb13ea1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
+          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist/ Data Architect</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Amy's Kitchen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Scientist/ Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Skillable</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
+          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
+          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer II - Cyber Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Skillable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
+          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
+          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Agentic AI Engineer II - Cyber Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
+          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
+          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gray Operations Group, Inc.</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Aberdeen, MD, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
+          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - Storage Specialist</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
+          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Gray Operations Group, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Aberdeen, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer – Identity Shield</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOLUTIONS ARCHITECT IV</t>
+          <t>AWS Cloud Engineer - Storage Specialist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Banda Group International</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
+          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
+          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Core Team</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FCP EURO</t>
+          <t>Userpilot</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>FCP EURO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
+          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect – Sales &amp; Marketing Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Performance Database Engineer</t>
+          <t>Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
+          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Application Architect (contract)</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Systems Integration Engineer 3</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UC San Diego</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kafka, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656b4089fd66ca54</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Integrations</t>
+          <t>Data Architect – Sales &amp; Marketing Technology</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
+          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Performance Database Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Application Architect (contract)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Systems Integration Engineer 3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Kafka, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
+          <t>https://www.indeed.com/viewjob?jk=656b4089fd66ca54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Full Stack Developer - Agri -Tech - US</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Sun World International, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
+          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
+          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Snowflake Data Warehouse Consultant</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AE Business Solutions</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
+          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Sr Data Engineer- Integrations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2547,11 +2547,11 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
+          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
         </is>
       </c>
     </row>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
         </is>
       </c>
     </row>
@@ -2678,20 +2678,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
+          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
+          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>System Architect – Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,400 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Snowflake Data Warehouse Consultant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AE Business Solutions</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>System Architect – Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5b974af9691c4f73</t>
         </is>

--- a/results/job_matches_2026-06-23.xlsx
+++ b/results/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Scientist/ Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e317b647d670c88</t>
+          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist/ Data Architect</t>
+          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
+          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
+          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
+          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer – Identity Shield</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gray Operations Group, Inc.</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Aberdeen, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dac14b064b52504</t>
+          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield</t>
+          <t>AWS Cloud Engineer - Storage Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
+          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - Storage Specialist</t>
+          <t>Senior Software Engineer - Core Team</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Userpilot</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
+          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Userpilot</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>FCP EURO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Milford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOLUTIONS ARCHITECT IV</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Banda Group International</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
+          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FCP EURO</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Milford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric (100% Remote)</t>
+          <t>Data Architect – Sales &amp; Marketing Technology</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
+          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Senior Performance Database Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Application Architect (contract)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect – Sales &amp; Marketing Technology</t>
+          <t>Senior Full Stack Developer - Agri -Tech - US</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Sun World International, LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Performance Database Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Architect (contract)</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
+          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Systems Integration Engineer 3</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UC San Diego</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kafka, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656b4089fd66ca54</t>
+          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Agri -Tech - US</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sun World International, LLC</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Sr Data Engineer- Integrations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
+          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Integrations</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
+          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
+          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Data Warehouse Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>AE Business Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
+          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
+          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
+          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3046,19 +3046,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
+          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3081,29 +3081,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
+          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
+          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
+          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Snowflake Data Warehouse Consultant</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AE Business Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
+          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
+          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>System Architect – Platform Engineering</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Solutions Architect - Strategic AI Natives</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>System Architect – Platform Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,392 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b974af9691c4f73</t>
+          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-23.xlsx
+++ b/results/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Skillable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Skillable</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
+          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer II - Cyber Analytics</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
+          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Agentic AI Engineer II - Cyber Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
+          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
+          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
+          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - Storage Specialist</t>
+          <t>Software Engineer – Identity Shield</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
+          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team</t>
+          <t>AWS Cloud Engineer - Storage Specialist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Userpilot</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
+          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Engineer - Core Team</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Userpilot</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SOLUTIONS ARCHITECT IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Banda Group International</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FCP EURO</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>FCP EURO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
+          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect – Sales &amp; Marketing Technology</t>
+          <t>Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Performance Database Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Architect (contract)</t>
+          <t>Data Architect – Sales &amp; Marketing Technology</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
+          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric (100% Remote)</t>
+          <t>Senior Performance Database Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
+          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Agri -Tech - US</t>
+          <t>Application Architect (contract)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sun World International, LLC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Senior Full Stack Developer - Agri -Tech - US</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Sun World International, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
+          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
         </is>
       </c>
     </row>
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Integrations</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
+          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Sr Data Engineer- Integrations</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
+          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
+          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
+          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Snowflake Data Warehouse Consultant</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AE Business Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
+          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
+          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
+          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
+          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3046,19 +3046,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3081,19 +3081,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3116,19 +3116,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,19 +3226,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
+          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
+          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Snowflake Data Warehouse Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>AE Business Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
+          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic AI Natives</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
+          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
+          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>System Architect – Platform Engineering</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,29 +3566,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,24 +3636,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Solutions Architect - Strategic AI Natives</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>System Architect – Platform Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
+          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
+          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,15 +3986,50 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
         </is>

--- a/results/job_matches_2026-06-23.xlsx
+++ b/results/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Houston Only</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fe3e1ce3f976c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd3b089b8e85de9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Database Engineer</t>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,252 +766,252 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1489cddaebca9c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=047ca970efc97204</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brownsville, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a768e6f7c8f1f47f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c64b08e271f522f6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
+          <t>Senior Full Stack Software Engineer - Claims Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
+          <t>https://www.indeed.com/viewjob?jk=26fefc6c4e81a9d3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
+          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amy's Kitchen</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea54597079589d42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist/ Data Architect</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brownsville, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
+          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer Associate - Full Stack (ETF Focused)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af2f21ad2271e214</t>
+          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skillable</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
+          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Amy's Kitchen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer II - Cyber Analytics</t>
+          <t>Data Scientist/ Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
+          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
+          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Skillable</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Databricks Architect with P&amp;C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
+          <t>https://www.indeed.com/viewjob?jk=f2920f81c9f2b0e5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
+          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Agentic AI Engineer II - Cyber Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
+          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
+          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - Storage Specialist</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5184de3aab6b232</t>
+          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Userpilot</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOLUTIONS ARCHITECT IV</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Banda Group International</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FCP EURO</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Milford, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer – Identity Shield</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
+          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Core Team</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Userpilot</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric (100% Remote)</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>FCP EURO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect – Sales &amp; Marketing Technology</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Performance Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4925c6e7012876a</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Application Architect (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4005e09738f87b</t>
+          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Agri -Tech - US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sun World International, LLC</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Seurat Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebb9ed44dd6b43d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c184380a5df33b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Architect – Sales &amp; Marketing Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Integrations</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
+          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Full Stack Developer - Agri -Tech - US</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>Sun World International, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=230f2097d39a709c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d897690a96d924bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfab581c91ff74c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer- Integrations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
+          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,172 +2736,172 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
+          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Snowflake Data Warehouse Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>AE Business Solutions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
+          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3116,19 +3116,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3151,19 +3151,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c328c7448124caa</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a2f833ade47dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a05c65027f02540</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea857b2446e2cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98a7522f331ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, ETL, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fa1a739f4dfcad</t>
+          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Snowflake Data Warehouse Consultant</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AE Business Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
+          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
+          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3536,29 +3536,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
+          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Red Bank, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=05fc6cb7a47df4b7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Senior Software Engineer, Payments</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
+          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
+          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
+          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic AI Natives</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>System Architect – Platform Engineering</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f81a3257ca39d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Solutions Architect - Strategic AI Natives</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619827434d7e7a20</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea59b60f49359e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Web Application Engineer (Irvine, US)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,50 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
         </is>

--- a/results/job_matches_2026-06-23.xlsx
+++ b/results/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c56ac0ca901604</t>
+          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Brownsville, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea54597079589d42</t>
+          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brownsville, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
+          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Amy's Kitchen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amy's Kitchen</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>Data Scientist/ Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist/ Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
+          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,29 +1291,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Skillable</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311fae6e7852845c</t>
+          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
         </is>
       </c>
     </row>
@@ -1413,25 +1413,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer II - Cyber Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>American Public Media</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705011c4830be681</t>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901037a80c58288a</t>
+          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf9fb3151d6e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ee45bf9eb0ffba</t>
+          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer – Identity Shield</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55836148ef2a5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4e7d744b937a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer - Core Team</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Userpilot</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a97de4c50830683</t>
+          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adcbc9e8685b739</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FCP EURO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Milford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Userpilot</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOLUTIONS ARCHITECT IV</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Banda Group International</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FCP EURO</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milford, CT, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7ab691a0b00d67</t>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Seurat Technologies</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, Photon, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1efe0d50d8101c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric (100% Remote)</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
         </is>
       </c>
     </row>
@@ -2463,35 +2463,35 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230f2097d39a709c</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfab581c91ff74c</t>
+          <t>https://www.indeed.com/viewjob?jk=230f2097d39a709c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfab581c91ff74c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Integrations</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
+          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Sr Data Engineer- Integrations</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
+          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>FuGen IT Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
+          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
+          <t>https://www.indeed.com/viewjob?jk=189e85b9aadd7294</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
+          <t>Sr. Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
+          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>INTELLIGENCE APPLICATION DEVELOPER</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>University of Alabama, Birmingham</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6fbff522d2790e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
+          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snowflake Data Warehouse Consultant</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AE Business Solutions</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
+          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,94 +3051,94 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb62f63f73a38c21</t>
+          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
+          <t>https://www.indeed.com/viewjob?jk=9167fc909538321d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Snowflake Data Warehouse Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>AE Business Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3291,19 +3291,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
+          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3326,19 +3326,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3361,19 +3361,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Red Bank, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05fc6cb7a47df4b7</t>
+          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,24 +3601,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3641,19 +3641,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3676,19 +3676,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Sr. Forward Deployed Engineer - Financial Services</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3711,29 +3711,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
+          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Senior Software Engineer, Payments</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Solutions Architect - Strategic AI Natives</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic AI Natives</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Red Bank, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
+          <t>https://www.indeed.com/viewjob?jk=05fc6cb7a47df4b7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
+          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Web Application Engineer (Irvine, US)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,15 +4056,190 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Web Application Engineer (Irvine, US)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Axon Networks</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
         </is>

--- a/results/job_matches_2026-06-23.xlsx
+++ b/results/job_matches_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
+          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
         </is>
       </c>
     </row>
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0995774c98d8f64</t>
+          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f0995774c98d8f64</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd3b089b8e85de9</t>
+          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047ca970efc97204</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>ClearpointCo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a768e6f7c8f1f47f</t>
+          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64b08e271f522f6</t>
+          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Claims Technology</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fefc6c4e81a9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
+          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brownsville, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65948e9315786e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, HBase, Spark, Scala, Oracle, SQL Server</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be023b7abd58b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Amy's Kitchen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
+          <t>Data Scientist/ Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,112 +1046,112 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
+          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amy's Kitchen</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist/ Data Architect</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Architect with P&amp;C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2920f81c9f2b0e5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,137 +1301,137 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Architect with P&amp;C</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2920f81c9f2b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Public Media</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e395960f5abda6</t>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,77 +1536,77 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=e718fc30d1d95fd0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Westwood, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
+          <t>https://www.indeed.com/viewjob?jk=6e08fb2784687034</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield</t>
+          <t>Senior Software Engineer - Core Team</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Userpilot</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b89b133a8ea2e09</t>
+          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Userpilot</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOLUTIONS ARCHITECT IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Banda Group International</t>
+          <t>FCP EURO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Milford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FCP EURO</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milford, CT, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Product Engineer (Software/Java)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1318e82a9a194375</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d5c06a29dc5f79</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Full Stack Developer - Agri -Tech - US</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Sun World International, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
+          <t>Data Architect – Sales &amp; Marketing Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
+          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect – Sales &amp; Marketing Technology</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric (100% Remote)</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,112 +2386,112 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Agri -Tech - US</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sun World International, LLC</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ebe8f7e65bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=230f2097d39a709c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230f2097d39a709c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfab581c91ff74c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfab581c91ff74c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb25f65aeae0c0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Integrations</t>
+          <t>Sr. Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6de5fb7f1d0546</t>
+          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>INTELLIGENCE APPLICATION DEVELOPER</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acima Leasing</t>
+          <t>University of Alabama, Birmingham</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5562bfd4f998c118</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6fbff522d2790e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, dbt, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ecf6407a53ab4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FuGen IT Solutions</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a0ca018ded67d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679b995b3aa9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189e85b9aadd7294</t>
+          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
+          <t>https://www.indeed.com/viewjob?jk=9167fc909538321d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>INTELLIGENCE APPLICATION DEVELOPER</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>University of Alabama, Birmingham</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6fbff522d2790e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,234 +2911,234 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
+          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394b99227e255a87</t>
+          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>829 Studios</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9167fc909538321d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Snowflake Data Warehouse Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>AE Business Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
+          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Snowflake Data Warehouse Consultant</t>
+          <t>Sr. Fullstack Engineer (Heavy backend/ AI-Assisted)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AE Business Solutions</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78b9627e2865de8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8e641f619c036a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecb9b0b3095edea</t>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
+          <t>Technology Operations Consultant for QRM BSM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+          <t>https://www.indeed.com/viewjob?jk=08dfee75b9d636ca</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Senior Software Engineer, Payments</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Solutions Architect - Strategic AI Natives</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Supervisor of Technical Product Development</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5604c52f06d0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=63c39e750667d68b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,24 +3461,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9d330852f409d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3501,19 +3501,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a3081bc81bfba1</t>
+          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3536,19 +3536,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded0c7a9dceb7dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3571,19 +3571,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860741b7d7b95265</t>
+          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3606,19 +3606,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223dc2b5127ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3641,19 +3641,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b9420fc6b40ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3676,19 +3676,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefa74af3d61ebf7</t>
+          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3711,29 +3711,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724915d9ab75c4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic AI Natives</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Web Application Engineer (Irvine, US)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Systems Administrator/Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Common Objects</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9d974e64a10e28</t>
+          <t>https://www.indeed.com/viewjob?jk=9b75462d74808ea8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Keenfinity</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Red Bank, TN, US USA</t>
+          <t>Fairport, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05fc6cb7a47df4b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7c7be3ac15aed</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+          <t>Senior IT. SecDevOps Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,332 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Business Analyst</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Web Application Engineer (Irvine, US)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Axon Networks</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=40347d597108dbff</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-23.xlsx
+++ b/results/job_matches_2026-06-23.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Automation Developer &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0394f69da3f3e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=8315a758255bb079</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0394f69da3f3e0c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,77 +556,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
+          <t>https://www.indeed.com/viewjob?jk=55ce642aeddf1f8f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Developer (Data Layer / API Specialist)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425ea68f605d30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,137 +636,137 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
+          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0995774c98d8f64</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Backend Developer (Data Layer / API Specialist)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
+          <t>https://www.indeed.com/viewjob?jk=425ea68f605d30dd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f0995774c98d8f64</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ClearpointCo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
+          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
+          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>ClearpointCo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
+          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
+          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amy's Kitchen</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist/ Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,139 +1046,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17be7a125f62a198</t>
+          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
+          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Amy's Kitchen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68f4aaf13a8c7f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Architect with P&amp;C</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2920f81c9f2b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b03f813a91fbdc2a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Architect with P&amp;C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Michigan City, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
+          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=f2920f81c9f2b0e5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>American Public Media</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e718fc30d1d95fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Westwood, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e08fb2784687034</t>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Userpilot</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262ca056c2ac8629</t>
+          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=e718fc30d1d95fd0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westwood, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=6e08fb2784687034</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FCP EURO</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Milford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOLUTIONS ARCHITECT IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Banda Group International</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
+          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>FCP EURO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, ETL, REST API integration, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e408e8968c4aede3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e7a2b148c2047</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>SOLUTIONS ARCHITECT IV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Banda Group International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala, Oracle, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=533e64be9b9768db</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Product Engineer (Software/Java)</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d5c06a29dc5f79</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Agri -Tech - US</t>
+          <t>Physical AI Engineering Consultant - Senior - Consulting - Open Location</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sun World International, LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, MLflow, CI/CD, Azure DevOps, AKS, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc25b2bad8f814d3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect – Sales &amp; Marketing Technology</t>
+          <t>Senior Full Stack Developer - Agri -Tech - US</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Sun World International, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f73e409f24d7f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>University of California - San Francisco</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, ETL, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b243686772972c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Sr. Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb25f65aeae0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Developer</t>
+          <t>INTELLIGENCE APPLICATION DEVELOPER</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>University of Alabama, Birmingham</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6fbff522d2790e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>INTELLIGENCE APPLICATION DEVELOPER</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of Alabama, Birmingham</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6fbff522d2790e</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb25f65aeae0c0</t>
         </is>
       </c>
     </row>
@@ -2883,42 +2883,42 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8022623046b6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>829 Studios</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>829 Studios</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
+          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Engineer (Heavy backend/ AI-Assisted)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8e641f619c036a</t>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Technology Operations Consultant for QRM BSM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+          <t>https://www.indeed.com/viewjob?jk=08dfee75b9d636ca</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant for QRM BSM</t>
+          <t>Senior Software Engineer, Payments</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dfee75b9d636ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Solutions Architect - Strategic AI Natives</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Architect - Strategic AI Natives</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bfc56c9a786d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Supervisor of Technical Product Development</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
+          <t>https://www.indeed.com/viewjob?jk=63c39e750667d68b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Supervisor of Technical Product Development</t>
+          <t>Sr. Fullstack Engineer (Heavy backend/ AI-Assisted)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c39e750667d68b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8e641f619c036a</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21b8846522997bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Web Application Engineer (Irvine, US)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Web Application Engineer (Irvine, US)</t>
+          <t>Systems Administrator/Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Common Objects</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+          <t>https://www.indeed.com/viewjob?jk=9b75462d74808ea8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Systems Administrator/Platform Engineer</t>
+          <t>Cloud Network Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Common Objects</t>
+          <t>Amerisure</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b75462d74808ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
         </is>
       </c>
     </row>
